--- a/df_fPC1/sum.var_AMR_ES_FQ_R.xlsx
+++ b/df_fPC1/sum.var_AMR_ES_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_AMC_EHPAD_totale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_AMC_ES_FQ</t>
   </si>
   <si>
     <t xml:space="preserve">log_AMC_ES_carba</t>
@@ -746,13 +743,10 @@
       <c r="BI1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" t="n">
         <v>0.00732955410328057</v>
@@ -782,165 +776,162 @@
         <v>-0.0519636488636131</v>
       </c>
       <c r="K2" t="n">
-        <v>0.10036063159044</v>
+        <v>0.0335610808107989</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0335610808107989</v>
+        <v>0.0553854830986644</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0553854830986644</v>
+        <v>0.0569453905067299</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0569453905067299</v>
+        <v>0.045746548313324</v>
       </c>
       <c r="O2" t="n">
-        <v>0.045746548313324</v>
+        <v>-0.0501690072424326</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0501690072424326</v>
+        <v>-0.119218369487267</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.119218369487267</v>
+        <v>-0.0899670434204568</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.0899670434204568</v>
+        <v>-0.0729740524328948</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0729740524328948</v>
+        <v>-0.0500340516551097</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0500340516551097</v>
+        <v>-0.110924482615121</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.110924482615121</v>
+        <v>-0.11340677064681</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.11340677064681</v>
+        <v>-0.0580919365243204</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0580919365243204</v>
+        <v>0.037870926705233</v>
       </c>
       <c r="X2" t="n">
-        <v>0.037870926705233</v>
+        <v>-0.114851315499916</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.114851315499916</v>
+        <v>0.0783652775785313</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0783652775785313</v>
+        <v>-0.00704050577408892</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.00704050577408892</v>
+        <v>-0.0332588684908322</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.0332588684908322</v>
+        <v>0.00732955410328057</v>
       </c>
       <c r="AC2" t="n">
+        <v>0.0582695830019245</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-12.3303494649166</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-4.38486917941033</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-18.8678731402826</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.130610908822835</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.375555392934203</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.357498405731887</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.152621661124171</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.150973298446975</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.346688833462624</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.235349613528001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.209548982113039</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0.00732955410328057</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0.0582695830019245</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-12.3303494649166</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-4.38486917941033</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-18.8678731402826</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.130610908822835</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.375555392934203</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.357498405731887</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.152621661124171</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.150973298446975</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-0.346688833462624</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.235349613528001</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-0.209548982113039</v>
-      </c>
       <c r="AP2" t="n">
+        <v>2.46131616730103</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-2.19227167052624</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.14689466098425</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.464358721866095</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11.0218902694913</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.0137138057235682</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0.00732955410328057</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>2.46131616730103</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-2.19227167052624</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-0.14689466098425</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.464358721866095</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>11.0218902694913</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-0.0137138057235682</v>
-      </c>
       <c r="AW2" t="n">
-        <v>0.00732955410328057</v>
+        <v>-0.0976156339794002</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.0976156339794002</v>
+        <v>0.0711842396775379</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0711842396775379</v>
+        <v>0.0133997267485429</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0133997267485429</v>
+        <v>-0.0134887005011725</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.0134887005011725</v>
+        <v>-0.0116735390973381</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.0116735390973381</v>
+        <v>-0.23814057256977</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.23814057256977</v>
+        <v>0.102157056829545</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.102157056829545</v>
+        <v>0.100964937158633</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.100964937158633</v>
+        <v>0.010521087269544</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.010521087269544</v>
+        <v>0.00535566593062078</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.00535566593062078</v>
+        <v>0.00172099403356767</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.00172099403356767</v>
+        <v>-0.00508228708977854</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.00508228708977854</v>
-      </c>
-      <c r="BJ2" t="n">
         <v>-0.073997723673461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" t="n">
         <v>-0.0448804961991626</v>
@@ -970,165 +961,162 @@
         <v>0.0110822982171971</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0352159793973484</v>
+        <v>-0.0975259174762126</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0975259174762126</v>
+        <v>0.127853592492332</v>
       </c>
       <c r="M3" t="n">
-        <v>0.127853592492332</v>
+        <v>0.0895718633627933</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0895718633627933</v>
+        <v>0.0890607105496024</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0890607105496024</v>
+        <v>-0.0113250537682787</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0113250537682787</v>
+        <v>0.0302138660849762</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0302138660849762</v>
+        <v>-0.0164060544761927</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0164060544761927</v>
+        <v>0.0138953877725435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0138953877725435</v>
+        <v>0.0264843564568429</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0264843564568429</v>
+        <v>0.0100861804927537</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0100861804927537</v>
+        <v>0.0155037622756563</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0155037622756563</v>
+        <v>0.0187351769509707</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0187351769509707</v>
+        <v>0.0966353497022475</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0966353497022475</v>
+        <v>0.0175382891813646</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0175382891813646</v>
+        <v>-0.0332510477570974</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0332510477570974</v>
+        <v>-0.0217683700198446</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.0217683700198446</v>
+        <v>0.0791304082566166</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0791304082566166</v>
+        <v>-0.0448804961991626</v>
       </c>
       <c r="AC3" t="n">
+        <v>-0.770302815554919</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.17771325978908</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>9.45590659332335</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>15.5290344904718</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0786333169234391</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.44603511539236</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.420761142313532</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.117825175411432</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.191019448211413</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.603686124644861</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.323806812980551</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.671327616035061</v>
+      </c>
+      <c r="AO3" t="n">
         <v>-0.0448804961991626</v>
       </c>
-      <c r="AD3" t="n">
-        <v>-0.770302815554919</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3.17771325978908</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.45590659332335</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>15.5290344904718</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.0786333169234391</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.44603511539236</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.420761142313532</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.117825175411432</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-0.191019448211413</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-0.603686124644861</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.323806812980551</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-0.671327616035061</v>
-      </c>
       <c r="AP3" t="n">
+        <v>-1.78849019467855</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.594774917323201</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.71738724827605</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.472378788154204</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-5.42457052529447</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.00784936955362009</v>
+      </c>
+      <c r="AV3" t="n">
         <v>-0.0448804961991626</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>-1.78849019467855</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.594774917323201</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-1.71738724827605</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-0.472378788154204</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-5.42457052529447</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-0.00784936955362009</v>
-      </c>
       <c r="AW3" t="n">
-        <v>-0.0448804961991626</v>
+        <v>-0.0689272219917101</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0689272219917101</v>
+        <v>-0.124494038406793</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.124494038406793</v>
+        <v>0.0396977072599543</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0396977072599543</v>
+        <v>-0.0114595398085665</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.0114595398085665</v>
+        <v>-0.00299484608859408</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.00299484608859408</v>
+        <v>-0.0900985847101783</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0900985847101783</v>
+        <v>-0.430405702605618</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.430405702605618</v>
+        <v>-0.0400073610756617</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0400073610756617</v>
+        <v>-0.0209620918427937</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0209620918427937</v>
+        <v>-0.00686645883417283</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.00686645883417283</v>
+        <v>-0.00212758389752027</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.00212758389752027</v>
+        <v>0.00960011029148658</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.00960011029148658</v>
-      </c>
-      <c r="BJ3" t="n">
         <v>-0.733223676197547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="n">
         <v>-0.0402427339189276</v>
@@ -1158,165 +1146,162 @@
         <v>-0.0181058995709713</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.278648268623139</v>
+        <v>-0.37338220636912</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.37338220636912</v>
+        <v>-0.205539145849943</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.205539145849943</v>
+        <v>-0.211568512897395</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.211568512897395</v>
+        <v>-0.204154783015747</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.204154783015747</v>
+        <v>-0.0988475340227592</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0988475340227592</v>
+        <v>-0.141210710616172</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.141210710616172</v>
+        <v>-0.0466720427614512</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0466720427614512</v>
+        <v>-0.0223308923262131</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0223308923262131</v>
+        <v>0.0503303137154591</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0503303137154591</v>
+        <v>-0.078711107427924</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.078711107427924</v>
+        <v>-0.0794524172790022</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0794524172790022</v>
+        <v>-0.00749851703955117</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.00749851703955117</v>
+        <v>-0.193174881389105</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.193174881389105</v>
+        <v>-0.0732747438842462</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.0732747438842462</v>
+        <v>0.114914367516149</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.114914367516149</v>
+        <v>-0.00278835022062918</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.00278835022062918</v>
+        <v>-0.0963687065038142</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.0963687065038142</v>
+        <v>-0.0402427339189276</v>
       </c>
       <c r="AC4" t="n">
+        <v>-0.0055179876751338</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-3.63618198377684</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3.19198075695889</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12.7284237561243</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.282585669768487</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.08459192358979</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.08405563486571</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.69130769280195</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.369642789809718</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.74556373901538</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.75630921144054</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.08339580005781</v>
+      </c>
+      <c r="AO4" t="n">
         <v>-0.0402427339189276</v>
       </c>
-      <c r="AD4" t="n">
-        <v>-0.0055179876751338</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-3.63618198377684</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3.19198075695889</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12.7284237561243</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.282585669768487</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.08459192358979</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.08405563486571</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.69130769280195</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-0.369642789809718</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2.74556373901538</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.75630921144054</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.08339580005781</v>
-      </c>
       <c r="AP4" t="n">
+        <v>-4.31875399729239</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.56540005694909</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.782589675263861</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-1.41801144666476</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-42.063917768553</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.00319752936881097</v>
+      </c>
+      <c r="AV4" t="n">
         <v>-0.0402427339189276</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>-4.31875399729239</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.56540005694909</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-0.782589675263861</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-1.41801144666476</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-42.063917768553</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.00319752936881097</v>
-      </c>
       <c r="AW4" t="n">
-        <v>-0.0402427339189276</v>
+        <v>0.391618492627779</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.391618492627779</v>
+        <v>-0.0654341902052057</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.0654341902052057</v>
+        <v>0.0180099487089462</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0180099487089462</v>
+        <v>-0.0322092704598475</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.0322092704598475</v>
+        <v>-0.017640294352863</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.017640294352863</v>
+        <v>0.271938752196663</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.271938752196663</v>
+        <v>0.0988875903309765</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0988875903309765</v>
+        <v>-0.110766501464643</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.110766501464643</v>
+        <v>-0.041946136308274</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.041946136308274</v>
+        <v>-0.00273756632938549</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.00273756632938549</v>
+        <v>-0.00197807540185887</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.00197807540185887</v>
+        <v>0.00639467520062348</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00639467520062348</v>
-      </c>
-      <c r="BJ4" t="n">
         <v>-0.00507901594179504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" t="n">
         <v>-0.00323860940402544</v>
@@ -1346,165 +1331,162 @@
         <v>-0.0943666974336294</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.046366232871423</v>
+        <v>-0.130678648965293</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.130678648965293</v>
+        <v>-0.0389749232001407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0389749232001407</v>
+        <v>-0.0666236764066978</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0666236764066978</v>
+        <v>-0.048917726788189</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.048917726788189</v>
+        <v>-0.026573481692435</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.026573481692435</v>
+        <v>-0.0692464942458135</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0692464942458135</v>
+        <v>-0.0647205616522289</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0647205616522289</v>
+        <v>-0.0278724541611876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0278724541611876</v>
+        <v>-0.0218776303200323</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0218776303200323</v>
+        <v>-0.0670574800503381</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0670574800503381</v>
+        <v>-0.0651659970916472</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0651659970916472</v>
+        <v>-0.094704517426158</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.094704517426158</v>
+        <v>-0.0493827395147707</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0493827395147707</v>
+        <v>-0.0662767394077226</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0662767394077226</v>
+        <v>0.0296737136920025</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0296737136920025</v>
+        <v>-0.0175848898050814</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0175848898050814</v>
+        <v>-0.000922632744525248</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.000922632744525248</v>
+        <v>-0.00323860940402544</v>
       </c>
       <c r="AC5" t="n">
+        <v>-0.602380310114915</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.8592769993275</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.192251643736603</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>26.77912495624</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.197700988707845</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.480525696225354</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.491243416945087</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.517661915067306</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.284096832305203</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.268031660005875</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.416594915570839</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.311494422645666</v>
+      </c>
+      <c r="AO5" t="n">
         <v>-0.00323860940402544</v>
       </c>
-      <c r="AD5" t="n">
-        <v>-0.602380310114915</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>12.8592769993275</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.192251643736603</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>26.77912495624</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.197700988707845</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.480525696225354</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.491243416945087</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.517661915067306</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-0.284096832305203</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-0.268031660005875</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-0.416594915570839</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-0.311494422645666</v>
-      </c>
       <c r="AP5" t="n">
+        <v>-3.27804295023073</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.103643179064499</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-1.31587084830012</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.38010878600959</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-6.61747476724499</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.0379833337977912</v>
+      </c>
+      <c r="AV5" t="n">
         <v>-0.00323860940402544</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>-3.27804295023073</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.103643179064499</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-1.31587084830012</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-0.38010878600959</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-6.61747476724499</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.0379833337977912</v>
-      </c>
       <c r="AW5" t="n">
-        <v>-0.00323860940402544</v>
+        <v>-0.0623337941018985</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0623337941018985</v>
+        <v>-0.0889789398903094</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.0889789398903094</v>
+        <v>0.0267904630273537</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0267904630273537</v>
+        <v>-0.011307532303508</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.011307532303508</v>
+        <v>0.000275088542728966</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.000275088542728966</v>
+        <v>-0.498774154428945</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.498774154428945</v>
+        <v>-0.805735820374807</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.805735820374807</v>
+        <v>-0.120788240069277</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.120788240069277</v>
+        <v>-0.0302881325843596</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.0302881325843596</v>
+        <v>0.0000407778520189205</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0000407778520189205</v>
+        <v>-0.000485969982432017</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.000485969982432017</v>
+        <v>0.00829966907346026</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00829966907346026</v>
-      </c>
-      <c r="BJ5" t="n">
         <v>-0.622655757258443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" t="n">
         <v>0.0196401513701033</v>
@@ -1534,165 +1516,162 @@
         <v>-0.00777819389424965</v>
       </c>
       <c r="K6" t="n">
-        <v>0.183072132285433</v>
+        <v>-0.0140515295826258</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0140515295826258</v>
+        <v>0.274774348068413</v>
       </c>
       <c r="M6" t="n">
-        <v>0.274774348068413</v>
+        <v>0.0577492007163787</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0577492007163787</v>
+        <v>0.085549861147115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.085549861147115</v>
+        <v>0.0581279308629707</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0581279308629707</v>
+        <v>0.0594315464166114</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0594315464166114</v>
+        <v>-0.0139516952096968</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0139516952096968</v>
+        <v>0.0972308094678789</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0972308094678789</v>
+        <v>-0.0395915370136168</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0395915370136168</v>
+        <v>0.0248045600792007</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0248045600792007</v>
+        <v>0.0291116808889536</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0291116808889536</v>
+        <v>-0.0130612761644817</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0130612761644817</v>
+        <v>0.070693667754269</v>
       </c>
       <c r="X6" t="n">
-        <v>0.070693667754269</v>
+        <v>0.0248295369766438</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0248295369766438</v>
+        <v>-0.0694984089622275</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0694984089622275</v>
+        <v>-0.0202219764604383</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0202219764604383</v>
+        <v>0.0597279019483435</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0597279019483435</v>
+        <v>0.0196401513701033</v>
       </c>
       <c r="AC6" t="n">
+        <v>-0.423678741868557</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2.61132807038946</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-6.89076795398724</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-29.9470519040486</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.0332608460612143</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.137839947010808</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.13637941094463</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.122399969203203</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.150794157450055</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.388364951192247</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.0224633016088872</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.595670602562299</v>
+      </c>
+      <c r="AO6" t="n">
         <v>0.0196401513701033</v>
       </c>
-      <c r="AD6" t="n">
-        <v>-0.423678741868557</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-2.61132807038946</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-6.89076795398724</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-29.9470519040486</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.0332608460612143</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.137839947010808</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.13637941094463</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-0.122399969203203</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.150794157450055</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-0.388364951192247</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-0.0224633016088872</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-0.595670602562299</v>
-      </c>
       <c r="AP6" t="n">
+        <v>0.647163158559724</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-3.1904011933925</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.453595963951475</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.622946781722748</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-15.8994468340273</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.00455811689816679</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0.0196401513701033</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>0.647163158559724</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-3.1904011933925</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.453595963951475</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.622946781722748</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-15.8994468340273</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.00455811689816679</v>
-      </c>
       <c r="AW6" t="n">
-        <v>0.0196401513701033</v>
+        <v>-0.0650535239568293</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0650535239568293</v>
+        <v>-0.0879917342022967</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0879917342022967</v>
+        <v>0.0198687079575747</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0198687079575747</v>
+        <v>0.00373493005830028</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.00373493005830028</v>
+        <v>0.00822729452788746</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.00822729452788746</v>
+        <v>0.0877323322809686</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0877323322809686</v>
+        <v>-0.190653634970529</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.190653634970529</v>
+        <v>0.0388954366948321</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0388954366948321</v>
+        <v>0.0118321019448495</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0118321019448495</v>
+        <v>-0.00503272571077103</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.00503272571077103</v>
+        <v>-0.000799265942887367</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.000799265942887367</v>
+        <v>-0.00593181281709199</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.00593181281709199</v>
-      </c>
-      <c r="BJ6" t="n">
         <v>-0.242091355144987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" t="n">
         <v>0.0188915953450621</v>
@@ -1722,165 +1701,162 @@
         <v>0.0918115939259928</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0601744798308835</v>
+        <v>-0.188331569638821</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.188331569638821</v>
+        <v>0.153377945552683</v>
       </c>
       <c r="M7" t="n">
-        <v>0.153377945552683</v>
+        <v>0.0199401871312824</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0199401871312824</v>
+        <v>0.0406597387657337</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0406597387657337</v>
+        <v>0.00202098858221799</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00202098858221799</v>
+        <v>0.0874935060532407</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0874935060532407</v>
+        <v>0.110979265869809</v>
       </c>
       <c r="R7" t="n">
-        <v>0.110979265869809</v>
+        <v>0.0239107660601627</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0239107660601627</v>
+        <v>0.00273469106055817</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00273469106055817</v>
+        <v>0.106006793938559</v>
       </c>
       <c r="U7" t="n">
-        <v>0.106006793938559</v>
+        <v>0.105554071475889</v>
       </c>
       <c r="V7" t="n">
-        <v>0.105554071475889</v>
+        <v>0.0951759245750315</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0951759245750315</v>
+        <v>0.0383246834572868</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0383246834572868</v>
+        <v>0.111511245163811</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.111511245163811</v>
+        <v>0.0276913164771287</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0276913164771287</v>
+        <v>-0.000156771078757567</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.000156771078757567</v>
+        <v>0.117467098864332</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.117467098864332</v>
+        <v>0.0188915953450621</v>
       </c>
       <c r="AC7" t="n">
+        <v>0.138826687668009</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-4.93482380993126</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-7.22063560926808</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>19.8455533951558</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.0180925555466997</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.418246721515095</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.424361583032095</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.289059744010996</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.271578415094269</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.308994584925497</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.159101834134017</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.197995368697023</v>
+      </c>
+      <c r="AO7" t="n">
         <v>0.0188915953450621</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0.138826687668009</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-4.93482380993126</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-7.22063560926808</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>19.8455533951558</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-0.0180925555466997</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.418246721515095</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.424361583032095</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.289059744010996</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-0.271578415094269</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.308994584925497</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.159101834134017</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.197995368697023</v>
-      </c>
       <c r="AP7" t="n">
+        <v>1.12134033295021</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-5.94298722785559</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.15545868450043</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.54602068082667</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-32.1995523411849</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.0121944982685219</v>
+      </c>
+      <c r="AV7" t="n">
         <v>0.0188915953450621</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>1.12134033295021</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-5.94298722785559</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.15545868450043</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.54602068082667</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-32.1995523411849</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-0.0121944982685219</v>
-      </c>
       <c r="AW7" t="n">
-        <v>0.0188915953450621</v>
+        <v>-0.170172304400208</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.170172304400208</v>
+        <v>-0.130900303696153</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.130900303696153</v>
+        <v>-0.0097474141827183</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.0097474141827183</v>
+        <v>0.0367801772712077</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0367801772712077</v>
+        <v>0.0262124964709996</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0262124964709996</v>
+        <v>0.357638558366775</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.357638558366775</v>
+        <v>-0.563513299647262</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.563513299647262</v>
+        <v>-0.106189643756344</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.106189643756344</v>
+        <v>-0.0501937303954304</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0501937303954304</v>
+        <v>0.0165749855340629</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0165749855340629</v>
+        <v>0.00341200918641746</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.00341200918641746</v>
+        <v>-0.0185588523633794</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.0185588523633794</v>
-      </c>
-      <c r="BJ7" t="n">
         <v>0.420820327277151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" t="n">
         <v>0.0533533633004615</v>
@@ -1910,165 +1886,162 @@
         <v>-0.0493917054781802</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0883645155060498</v>
+        <v>0.309219299525867</v>
       </c>
       <c r="L8" t="n">
-        <v>0.309219299525867</v>
+        <v>-0.0594563130241014</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0594563130241014</v>
+        <v>0.0689130477673912</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0689130477673912</v>
+        <v>0.0567337331081234</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0567337331081234</v>
+        <v>-0.0463280683589995</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0463280683589995</v>
+        <v>0.0138111941148235</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0138111941148235</v>
+        <v>0.0861825699207249</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0861825699207249</v>
+        <v>0.263100653547779</v>
       </c>
       <c r="S8" t="n">
-        <v>0.263100653547779</v>
+        <v>0.0241502037875185</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0241502037875185</v>
+        <v>0.0973588798247507</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0973588798247507</v>
+        <v>0.0823716821161474</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0823716821161474</v>
+        <v>-0.0423401208623003</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0423401208623003</v>
+        <v>0.0757260764774565</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0757260764774565</v>
+        <v>0.0918117366690664</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0918117366690664</v>
+        <v>0.00189803511554691</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00189803511554691</v>
+        <v>0.0317868662453055</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0317868662453055</v>
+        <v>-0.0612103131719041</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.0612103131719041</v>
+        <v>0.0533533633004615</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.71905337412741</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-9.01272307721351</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-16.3377612856515</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-92.0387708878531</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.324050522133134</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.96214937859133</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.89546618886632</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-1.89651190208578</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.537245017539383</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-1.22021097105653</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1.22631695627796</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.810419476847576</v>
+      </c>
+      <c r="AO8" t="n">
         <v>0.0533533633004615</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.71905337412741</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-9.01272307721351</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-16.3377612856515</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-92.0387708878531</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.324050522133134</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-1.96214937859133</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-1.89546618886632</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-1.89651190208578</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-0.537245017539383</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1.22021097105653</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-1.22631695627796</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-0.810419476847576</v>
-      </c>
       <c r="AP8" t="n">
+        <v>11.0611048510848</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-8.13657157043532</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.89965622981696</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.2231669853248</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-14.3772288344109</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.0167786207189275</v>
+      </c>
+      <c r="AV8" t="n">
         <v>0.0533533633004615</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>11.0611048510848</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-8.13657157043532</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.89965622981696</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.2231669853248</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-14.3772288344109</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.0167786207189275</v>
-      </c>
       <c r="AW8" t="n">
-        <v>0.0533533633004615</v>
+        <v>-0.160721921099835</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.160721921099835</v>
+        <v>0.623368914024887</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.623368914024887</v>
+        <v>-0.104572526869896</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.104572526869896</v>
+        <v>0.0145650987656854</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0145650987656854</v>
+        <v>-0.00235061950876203</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0.00235061950876203</v>
+        <v>-0.364227869492569</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.364227869492569</v>
+        <v>0.868083983240932</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.868083983240932</v>
+        <v>0.332517882452744</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.332517882452744</v>
+        <v>0.103648576807794</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.103648576807794</v>
+        <v>0.0175497742443751</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0175497742443751</v>
+        <v>0.00697314120095147</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.00697314120095147</v>
+        <v>-0.0301335771134524</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0.0301335771134524</v>
-      </c>
-      <c r="BJ8" t="n">
         <v>2.10000862327134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" t="n">
         <v>-0.0383343059783089</v>
@@ -2098,165 +2071,162 @@
         <v>0.0855536155303945</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0504734259398501</v>
+        <v>-0.208271122741779</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.208271122741779</v>
+        <v>-0.0460661464046912</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0460661464046912</v>
+        <v>0.142574713819131</v>
       </c>
       <c r="N9" t="n">
-        <v>0.142574713819131</v>
+        <v>0.0986245611203094</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0986245611203094</v>
+        <v>-0.0108437631294407</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0108437631294407</v>
+        <v>0.0786633420934962</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0786633420934962</v>
+        <v>0.0415623718171625</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0415623718171625</v>
+        <v>-0.0324191136737228</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0324191136737228</v>
+        <v>-0.0027053805893549</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0027053805893549</v>
+        <v>0.0353936440864668</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0353936440864668</v>
+        <v>0.0383287535447493</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0383287535447493</v>
+        <v>0.09066077539429</v>
       </c>
       <c r="W9" t="n">
-        <v>0.09066077539429</v>
+        <v>0.104722423510447</v>
       </c>
       <c r="X9" t="n">
-        <v>0.104722423510447</v>
+        <v>0.0416848994848347</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0416848994848347</v>
+        <v>0.0247461477456109</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0247461477456109</v>
+        <v>-0.00113998729489261</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.00113998729489261</v>
+        <v>-0.0674828256708319</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.0674828256708319</v>
+        <v>-0.0383343059783089</v>
       </c>
       <c r="AC9" t="n">
+        <v>-0.314908419026853</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.624784079803963</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>24.7971160064304</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>21.1224527119021</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.229753807778225</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.05828541957378</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.06438261422827</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.785942009562261</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.239068858776235</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.487882730365099</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.697195612240213</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.0374455911788562</v>
+      </c>
+      <c r="AO9" t="n">
         <v>-0.0383343059783089</v>
       </c>
-      <c r="AD9" t="n">
-        <v>-0.314908419026853</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.624784079803963</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>24.7971160064304</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>21.1224527119021</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.229753807778225</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.05828541957378</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.06438261422827</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.785942009562261</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-0.239068858776235</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.487882730365099</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0.697195612240213</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-0.0374455911788562</v>
-      </c>
       <c r="AP9" t="n">
+        <v>-1.67028852900829</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.0109312412913779</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.191921675231057</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.336248048840461</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-38.3424138223202</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.00107446016607559</v>
+      </c>
+      <c r="AV9" t="n">
         <v>-0.0383343059783089</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>-1.67028852900829</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-0.0109312412913779</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.191921675231057</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.336248048840461</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-38.3424138223202</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-0.00107446016607559</v>
-      </c>
       <c r="AW9" t="n">
-        <v>-0.0383343059783089</v>
+        <v>0.074872943332801</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.074872943332801</v>
+        <v>-0.085804112752481</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.085804112752481</v>
+        <v>0.0321586612015137</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0321586612015137</v>
+        <v>-0.00673117719952007</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.00673117719952007</v>
+        <v>0.00173258813346108</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.00173258813346108</v>
+        <v>-0.0206447053958451</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.0206447053958451</v>
+        <v>-0.56047013214129</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.56047013214129</v>
+        <v>-0.0657887445398481</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.0657887445398481</v>
+        <v>-0.0496410442958685</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.0496410442958685</v>
+        <v>0.00197200880993254</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.00197200880993254</v>
+        <v>-0.000229650166180577</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.000229650166180577</v>
+        <v>0.000208184884516435</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.000208184884516435</v>
-      </c>
-      <c r="BJ9" t="n">
         <v>-0.10211662579286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="n">
         <v>-0.00601199919180279</v>
@@ -2286,165 +2256,162 @@
         <v>0.0705558338791445</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0849547857042242</v>
+        <v>0.0601430323680632</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0601430323680632</v>
+        <v>-0.00043433221317463</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.00043433221317463</v>
+        <v>0.0429291520748785</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0429291520748785</v>
+        <v>0.0292138845299469</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0292138845299469</v>
+        <v>0.0660182326205712</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0660182326205712</v>
+        <v>0.00620438066090511</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.00620438066090511</v>
+        <v>0.0307882196430586</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0307882196430586</v>
+        <v>-0.0506951096157239</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0506951096157239</v>
+        <v>0.013325731189545</v>
       </c>
       <c r="T10" t="n">
-        <v>0.013325731189545</v>
+        <v>0.0243370745759228</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0243370745759228</v>
+        <v>0.0325507305764863</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0325507305764863</v>
+        <v>0.0637311713530358</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0637311713530358</v>
+        <v>0.0218218940632773</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0218218940632773</v>
+        <v>0.0274333514639498</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0274333514639498</v>
+        <v>-0.0338589119520969</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0338589119520969</v>
+        <v>-0.00351881208243151</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.00351881208243151</v>
+        <v>0.000139235351569367</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.000139235351569367</v>
+        <v>-0.00601199919180279</v>
       </c>
       <c r="AC10" t="n">
+        <v>-0.317730159419209</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>9.18564175834393</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.60351806295416</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>38.9228280039465</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.0079908077062404</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.0993371854900619</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.0648298521035288</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.120572232824682</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.598748291963005</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.117960350491315</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.0824821535077846</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.322043412432475</v>
+      </c>
+      <c r="AO10" t="n">
         <v>-0.00601199919180279</v>
       </c>
-      <c r="AD10" t="n">
-        <v>-0.317730159419209</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>9.18564175834393</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.60351806295416</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>38.9228280039465</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.0079908077062404</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.0993371854900619</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.0648298521035288</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.120572232824682</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0.598748291963005</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-0.117960350491315</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.0824821535077846</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.322043412432475</v>
-      </c>
       <c r="AP10" t="n">
+        <v>-3.36054905774655</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.125640023711585</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.05862112080309</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.969569942067806</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>20.4716391934634</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.00616639835771458</v>
+      </c>
+      <c r="AV10" t="n">
         <v>-0.00601199919180279</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>-3.36054905774655</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.125640023711585</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-1.05862112080309</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-0.969569942067806</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>20.4716391934634</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.00616639835771458</v>
-      </c>
       <c r="AW10" t="n">
-        <v>-0.00601199919180279</v>
+        <v>0.123513363905274</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.123513363905274</v>
+        <v>-0.0682606175468987</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.0682606175468987</v>
+        <v>0.00640762906621618</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.00640762906621618</v>
+        <v>-0.00569589876732141</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.00569589876732141</v>
+        <v>-0.00231622520835979</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.00231622520835979</v>
+        <v>0.226721715917034</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.226721715917034</v>
+        <v>0.255688366175892</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.255688366175892</v>
+        <v>-0.106329782035779</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.106329782035779</v>
+        <v>0.000487602492993006</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.000487602492993006</v>
+        <v>-0.01638452748375</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.01638452748375</v>
+        <v>-0.00423125097371813</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.00423125097371813</v>
+        <v>0.0154679259900934</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0154679259900934</v>
-      </c>
-      <c r="BJ10" t="n">
         <v>-0.544121789461287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" t="n">
         <v>0.0190675251908354</v>
@@ -2474,165 +2441,162 @@
         <v>0.0296954906944263</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0158617624856274</v>
+        <v>0.313060253546427</v>
       </c>
       <c r="L11" t="n">
-        <v>0.313060253546427</v>
+        <v>0.00626647960588356</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00626647960588356</v>
+        <v>-0.0774613195443716</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0774613195443716</v>
+        <v>-0.0427652547046527</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0427652547046527</v>
+        <v>0.109958567821692</v>
       </c>
       <c r="P11" t="n">
-        <v>0.109958567821692</v>
+        <v>0.042769586516405</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.042769586516405</v>
+        <v>0.0211958266043548</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0211958266043548</v>
+        <v>-0.0434899261813493</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0434899261813493</v>
+        <v>-0.000646349904212877</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.000646349904212877</v>
+        <v>0.0320732469906415</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0320732469906415</v>
+        <v>0.03321280075391</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03321280075391</v>
+        <v>0.0240534255699838</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0240534255699838</v>
+        <v>-0.0505408090917457</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.0505408090917457</v>
+        <v>0.0233233898465209</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0233233898465209</v>
+        <v>-0.134269002145114</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.134269002145114</v>
+        <v>-0.0160402896903781</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.0160402896903781</v>
+        <v>0.1346138312419</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1346138312419</v>
+        <v>0.0190675251908354</v>
       </c>
       <c r="AC11" t="n">
+        <v>0.128949509529747</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>6.42513956495643</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-3.78655200623572</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>28.9449742236903</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.0951203534760066</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.280465339930393</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.315517269456471</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.268724626977033</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.975430705687471</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.489446482450284</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.198475120765655</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.48313178901756</v>
+      </c>
+      <c r="AO11" t="n">
         <v>0.0190675251908354</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0.128949509529747</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>6.42513956495643</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-3.78655200623572</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>28.9449742236903</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.0951203534760066</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-0.280465339930393</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.315517269456471</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-0.268724626977033</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0.975430705687471</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-0.489446482450284</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-0.198475120765655</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-0.48313178901756</v>
-      </c>
       <c r="AP11" t="n">
+        <v>-1.42640909208072</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.91211095973774</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.895613718645758</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.823422918814776</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>64.7608500031866</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.00583898559699208</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0.0190675251908354</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>-1.42640909208072</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.91211095973774</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-0.895613718645758</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-0.823422918814776</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>64.7608500031866</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-0.00583898559699208</v>
-      </c>
       <c r="AW11" t="n">
-        <v>0.0190675251908354</v>
+        <v>0.0725586485713087</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0725586485713087</v>
+        <v>-0.0794686588701281</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.0794686588701281</v>
+        <v>-0.022730959003571</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.022730959003571</v>
+        <v>0.028768876407479</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.028768876407479</v>
+        <v>0.00562799823828984</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.00562799823828984</v>
+        <v>0.132832947960337</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.132832947960337</v>
+        <v>0.482211586012499</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.482211586012499</v>
+        <v>-0.00974559752949912</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.00974559752949912</v>
+        <v>0.0316327784762719</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0316327784762719</v>
+        <v>-0.0103886763340441</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.0103886763340441</v>
+        <v>-0.00230109366776357</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.00230109366776357</v>
+        <v>0.00888449742549417</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.00888449742549417</v>
-      </c>
-      <c r="BJ11" t="n">
         <v>-0.416902965091475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" t="n">
         <v>0.0344414747163138</v>
@@ -2662,165 +2626,162 @@
         <v>0.0663592388653425</v>
       </c>
       <c r="K12" t="n">
-        <v>0.12082021118173</v>
+        <v>0.467253145695357</v>
       </c>
       <c r="L12" t="n">
-        <v>0.467253145695357</v>
+        <v>0.0242133243701543</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0242133243701543</v>
+        <v>0.00494770660750392</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00494770660750392</v>
+        <v>0.0122705756134747</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0122705756134747</v>
+        <v>0.131205113193585</v>
       </c>
       <c r="P12" t="n">
-        <v>0.131205113193585</v>
+        <v>0.198025239949699</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.198025239949699</v>
+        <v>0.0571106148616265</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0571106148616265</v>
+        <v>-0.00197631555638445</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.00197631555638445</v>
+        <v>0.0331111192044257</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0331111192044257</v>
+        <v>0.0984531138090642</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0984531138090642</v>
+        <v>0.094141686407852</v>
       </c>
       <c r="V12" t="n">
-        <v>0.094141686407852</v>
+        <v>0.0506071158844021</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0506071158844021</v>
+        <v>-0.00172738073185696</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.00172738073185696</v>
+        <v>0.0855989607660336</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0855989607660336</v>
+        <v>-0.193983119750397</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.193983119750397</v>
+        <v>0.0325476245037432</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0325476245037432</v>
+        <v>-0.0634160524993205</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.0634160524993205</v>
+        <v>0.0344414747163138</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.02430888453424</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.3825789897294</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-11.8074921105374</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-12.7054687916566</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.280826175534107</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.96187907500934</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.89482506440636</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-1.59565512176468</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.615213205875665</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-1.18205595693551</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1.22766947552045</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1.35410658786014</v>
+      </c>
+      <c r="AO12" t="n">
         <v>0.0344414747163138</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.02430888453424</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>10.3825789897294</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-11.8074921105374</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-12.7054687916566</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-0.280826175534107</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-1.96187907500934</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>-1.89482506440636</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-1.59565512176468</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0.615213205875665</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-1.18205595693551</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-1.22766947552045</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-1.35410658786014</v>
-      </c>
       <c r="AP12" t="n">
+        <v>4.24082559502784</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.72187461778694</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.20570944017448</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.13064796511604</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>69.5078139826724</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-0.0128544574122275</v>
+      </c>
+      <c r="AV12" t="n">
         <v>0.0344414747163138</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>4.24082559502784</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>6.72187461778694</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.20570944017448</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.13064796511604</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>69.5078139826724</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-0.0128544574122275</v>
-      </c>
       <c r="AW12" t="n">
-        <v>0.0344414747163138</v>
+        <v>-0.25086384606443</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.25086384606443</v>
+        <v>0.0495522387392417</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0495522387392417</v>
+        <v>-0.0605144058354366</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.0605144058354366</v>
+        <v>0.0302788951199366</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0302788951199366</v>
+        <v>0.0059130078110877</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0059130078110877</v>
+        <v>0.283442369376223</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.283442369376223</v>
+        <v>1.25678752951199</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.25678752951199</v>
+        <v>0.198449042386782</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.198449042386782</v>
+        <v>0.0696894773037612</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0696894773037612</v>
+        <v>-0.00942422520285237</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.00942422520285237</v>
+        <v>-0.00110592499070373</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.00110592499070373</v>
+        <v>0.0122694085372572</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0122694085372572</v>
-      </c>
-      <c r="BJ12" t="n">
         <v>0.265324252837569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" t="n">
         <v>-0.0200155193338293</v>
@@ -2850,159 +2811,156 @@
         <v>-0.133451925871853</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.237554391414924</v>
+        <v>-0.170995817172662</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.170995817172662</v>
+        <v>-0.29140031249608</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.29140031249608</v>
+        <v>-0.127917753137626</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.127917753137626</v>
+        <v>-0.162021848639044</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.162021848639044</v>
+        <v>-0.123243924866692</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.123243924866692</v>
+        <v>-0.186937087540904</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.186937087540904</v>
+        <v>-0.116101471196711</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.116101471196711</v>
+        <v>-0.146379752900888</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.146379752900888</v>
+        <v>-0.0352814659320229</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0352814659320229</v>
+        <v>-0.171820423703977</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.171820423703977</v>
+        <v>-0.172749983022184</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.172749983022184</v>
+        <v>-0.127267221710903</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.127267221710903</v>
+        <v>-0.150969210942737</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.150969210942737</v>
+        <v>-0.16932861076034</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.16932861076034</v>
+        <v>0.187571632441963</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.187571632441963</v>
+        <v>0.0259254616774935</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0259254616774935</v>
+        <v>-0.0684190765815336</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.0684190765815336</v>
+        <v>-0.0200155193338293</v>
       </c>
       <c r="AC13" t="n">
+        <v>-0.63488960520175</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-8.88016008611467</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>10.5718083691601</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-10.3132268136898</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.235458545872261</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.06512778425032</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.04478329645459</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.2436250193625</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.296919982786842</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.07400427593327</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.837274531912688</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.8697104870729</v>
+      </c>
+      <c r="AO13" t="n">
         <v>-0.0200155193338293</v>
       </c>
-      <c r="AD13" t="n">
-        <v>-0.63488960520175</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-8.88016008611467</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>10.5718083691601</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-10.3132268136898</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.235458545872261</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.06512778425032</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.04478329645459</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.2436250193625</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>-0.296919982786842</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.07400427593327</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0.837274531912688</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1.8697104870729</v>
-      </c>
       <c r="AP13" t="n">
+        <v>-3.68921628388639</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.44971914892797</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.698329443036231</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.587401204304756</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-10.837588555778</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.00604218862407214</v>
+      </c>
+      <c r="AV13" t="n">
         <v>-0.0200155193338293</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>-3.68921628388639</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.44971914892797</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-0.698329443036231</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-0.587401204304756</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-10.837588555778</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-0.00604218862407214</v>
-      </c>
       <c r="AW13" t="n">
-        <v>-0.0200155193338293</v>
+        <v>0.213124797157149</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.213124797157149</v>
+        <v>-0.0127727968714012</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.0127727968714012</v>
+        <v>0.0412324619215205</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0412324619215205</v>
+        <v>-0.0332358585826731</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.0332358585826731</v>
+        <v>-0.0110129494685375</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.0110129494685375</v>
+        <v>-0.148420789500691</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0.148420789500691</v>
+        <v>-0.513037522362324</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.513037522362324</v>
+        <v>-0.11121142822194</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.11121142822194</v>
+        <v>-0.0347804888684874</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.0347804888684874</v>
+        <v>0.00934096752396569</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.00934096752396569</v>
+        <v>0.00115267060212793</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.00115267060212793</v>
+        <v>-0.00141794201922911</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0.00141794201922911</v>
-      </c>
-      <c r="BJ13" t="n">
         <v>-0.0459642948242026</v>
       </c>
     </row>
